--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.04553244631661</v>
+        <v>6.994899022526448</v>
       </c>
       <c r="D2" t="n">
-        <v>43.08881388205076</v>
+        <v>7.00193225583325</v>
       </c>
       <c r="E2" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F2" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.34674754481387</v>
+        <v>7.856346476032254</v>
       </c>
       <c r="D3" t="n">
-        <v>48.38080754893336</v>
+        <v>7.861881226701672</v>
       </c>
       <c r="E3" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F3" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.90810857097838</v>
+        <v>5.022567642783987</v>
       </c>
       <c r="D4" t="n">
-        <v>30.98776307935049</v>
+        <v>5.035511500394454</v>
       </c>
       <c r="E4" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F4" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.92604667101642</v>
+        <v>6.812982584040169</v>
       </c>
       <c r="D5" t="n">
-        <v>41.92849293465087</v>
+        <v>6.813380101880766</v>
       </c>
       <c r="E5" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F5" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.89147492213289</v>
+        <v>6.482364674846595</v>
       </c>
       <c r="D6" t="n">
-        <v>39.92633527097694</v>
+        <v>6.488029481533752</v>
       </c>
       <c r="E6" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F6" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.74346725807059</v>
+        <v>6.295813429436471</v>
       </c>
       <c r="D7" t="n">
-        <v>38.70932684093633</v>
+        <v>6.290265611652154</v>
       </c>
       <c r="E7" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F7" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.53754946580086</v>
+        <v>3.98735178819264</v>
       </c>
       <c r="D8" t="n">
-        <v>24.48874960360394</v>
+        <v>3.97942181058564</v>
       </c>
       <c r="E8" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F8" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.59583359265003</v>
+        <v>5.94682295880563</v>
       </c>
       <c r="D9" t="n">
-        <v>36.57517024413299</v>
+        <v>5.943465164671611</v>
       </c>
       <c r="E9" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F9" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.63136018842895</v>
+        <v>4.490096030619704</v>
       </c>
       <c r="D10" t="n">
-        <v>27.54901360617136</v>
+        <v>4.476714711002845</v>
       </c>
       <c r="E10" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F10" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.75122379541619</v>
+        <v>4.997073866755132</v>
       </c>
       <c r="D11" t="n">
-        <v>30.6917205994508</v>
+        <v>4.987404597410754</v>
       </c>
       <c r="E11" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F11" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.52751788601646</v>
+        <v>7.885721656477675</v>
       </c>
       <c r="D12" t="n">
-        <v>48.49750230748406</v>
+        <v>7.880844124966161</v>
       </c>
       <c r="E12" t="n">
-        <v>7.698091001982078</v>
+        <v>1.250939787822088</v>
       </c>
       <c r="F12" t="n">
-        <v>7.71780418373125</v>
+        <v>1.254143179856328</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
